--- a/assets/constructions/examples/ctd_rm1.xlsx
+++ b/assets/constructions/examples/ctd_rm1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,31 +669,56 @@
           <t>brazed</t>
         </is>
       </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HMAL31D13.17XTS</t>
+          <t>RCL6.1153HTN.STE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FRESAL</t>
+          <t>BRICE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HMAL31</t>
+          <t>Brice развертки</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PKN</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>13.17</v>
+        <v>11.53</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -703,44 +728,30 @@
         <v>0.005</v>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0,005</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
-      </c>
-      <c r="P2" t="n">
-        <v>52</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>12</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="U2" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -750,11 +761,9 @@
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>28</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
@@ -767,24 +776,18 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>45</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>HM HartMetal</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>HM HartMetal</t>
-        </is>
-      </c>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -803,11 +806,7 @@
           <t>L</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>DIN 8089</t>
-        </is>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
@@ -817,7 +816,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>AL 019.01 GB</t>
+          <t>2022/BRICE</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -830,32 +829,43 @@
       </c>
       <c r="AV2" t="b">
         <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HMAL28D13.38</t>
+          <t>6326C-d9.78</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FRESAL</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HMAL28</t>
+          <t>6326C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PKN</t>
+          <t>PMKNS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>13.38</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
@@ -865,44 +875,32 @@
         <v>0.005</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0,005</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>8</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>195</v>
-      </c>
-      <c r="P3" t="n">
-        <v>75</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h9</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>270</v>
+        <v>133</v>
       </c>
       <c r="U3" t="n">
-        <v>270</v>
+        <v>133</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -912,11 +910,9 @@
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>195</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
@@ -929,9 +925,7 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>45</v>
-      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -939,21 +933,21 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>HM HartMetal</t>
+          <t>HSS-CO</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>HM HartMetal</t>
+          <t>HSS-CO</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -967,7 +961,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>FRESAL NORM</t>
+          <t>DIN 212 B/D</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr"/>
@@ -979,12 +973,12 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>AL 019.01 GB</t>
+          <t>2019-katalog.pdf</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>THROUGH</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="AU3" t="b">
@@ -992,12 +986,23 @@
       </c>
       <c r="AV3" t="b">
         <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HMAL31D15.18</t>
+          <t>AL28D09.03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1007,7 +1012,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HMAL31</t>
+          <t>AL28</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1017,7 +1022,7 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>15.18</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
@@ -1039,17 +1044,17 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="P4" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1057,14 +1062,14 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="U4" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-9</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1074,10 +1079,10 @@
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1101,17 +1106,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>HM HartMetal</t>
+          <t>HSS-V</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>HM HartMetal</t>
+          <t>HSS-V</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1129,7 +1134,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>DIN 8089</t>
+          <t>FRESAL NORM</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr"/>
@@ -1155,11 +1160,30 @@
       <c r="AV4" t="b">
         <v>0</v>
       </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>170.67</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15690.32</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AL15D10.78</t>
+          <t>HMAL28D14.44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1169,7 +1193,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AL15</t>
+          <t>HMAL28</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1179,7 +1203,7 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>10.78</v>
+        <v>14.44</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
@@ -1201,17 +1225,17 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>10.78</v>
+        <v>15</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1219,14 +1243,14 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="U5" t="n">
-        <v>142</v>
+        <v>280</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>HS-10.78</t>
+          <t>HA-15</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1236,10 +1260,10 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="Z5" t="n">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1263,17 +1287,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>HSS-V</t>
+          <t>HM HartMetal</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HSS-V</t>
+          <t>HM HartMetal</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,7 +1305,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1291,7 +1315,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>DIN 206B</t>
+          <t>FRESAL NORM</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr"/>
@@ -1317,11 +1341,30 @@
       <c r="AV5" t="b">
         <v>0</v>
       </c>
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1296.8</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>119219.62</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AL15D09.74XTS</t>
+          <t>HMAL25D05.50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1331,7 +1374,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AL15</t>
+          <t>HMAL25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1341,14 +1384,14 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>9.74</v>
+        <v>5.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
@@ -1358,7 +1401,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0,005</t>
+          <t>0,004</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1366,14 +1409,14 @@
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="P6" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>9.74</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1381,14 +1424,14 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="U6" t="n">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>HS-9.74</t>
+          <t>HA-5</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1398,10 +1441,10 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1420,22 +1463,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>HSS-V</t>
+          <t>HM HartMetal</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HSS-V</t>
+          <t>HM HartMetal</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1443,7 +1486,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1453,7 +1496,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>DIN 206B</t>
+          <t>DIN 212B/DIN 212D</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr"/>
@@ -1479,6 +1522,25 @@
       <c r="AV6" t="b">
         <v>0</v>
       </c>
+      <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>143.36</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13179.62</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
